--- a/data/mock_regex.xlsx
+++ b/data/mock_regex.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lila_\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE1CA0E0-8D83-44FE-A574-DEA71F83E9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AF575E-AA1F-42FD-8118-E728C807F2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DF677BBC-BDCC-419E-8C4C-B011E30DC112}"/>
   </bookViews>
   <sheets>
-    <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
+    <sheet name="Arkusz1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t>Field</t>
   </si>
@@ -208,9 +208,6 @@
     <t>Generated based on Requester ID.</t>
   </si>
   <si>
-    <t>equester Mail</t>
-  </si>
-  <si>
     <t>Requester Email Address</t>
   </si>
   <si>
@@ -259,63 +256,6 @@
     <t>Random value in the range 100–20000.</t>
   </si>
   <si>
-    <t>Invoice Number</t>
-  </si>
-  <si>
-    <t>String (15 letters/numbers)</t>
-  </si>
-  <si>
-    <t>FV/2026/12/0914</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Unique value starting with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>FV/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> + year/month + random 4‑digit number.</t>
-    </r>
-  </si>
-  <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
-    <t>Always after the delivery date.</t>
-  </si>
-  <si>
-    <t>Invoice Status</t>
-  </si>
-  <si>
-    <t>Enum (entered, hold, paid, pending ap)</t>
-  </si>
-  <si>
-    <t>entered</t>
-  </si>
-  <si>
-    <t>Value selected from invoice workflow statuses.</t>
-  </si>
-  <si>
-    <t>Invoice Amount</t>
-  </si>
-  <si>
-    <t>Usually equal to PO Amount; may differ by ±5%.</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -335,6 +275,15 @@
   </si>
   <si>
     <t>Number of days to payment, random value 15–90.</t>
+  </si>
+  <si>
+    <t>Requester Mail</t>
+  </si>
+  <si>
+    <t>Create Date</t>
+  </si>
+  <si>
+    <t>Random date within the time frame</t>
   </si>
 </sst>
 </file>
@@ -799,18 +748,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669912DB-2E8B-4A93-9D70-0978DEE186A1}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F5A8C8E-2293-440B-AA5D-AD93DAA2CFD9}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="46.77734375" customWidth="1"/>
+    <col min="1" max="1" width="27.5546875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="28.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -844,7 +793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="63" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -861,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -895,7 +844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -929,174 +878,123 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D9" s="3">
         <v>46106</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46106</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1520</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1520</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="3">
-        <v>46185</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D14" s="2">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1520</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="2">
-        <v>79</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
